--- a/outputs/busca_saúde_coletiva.xlsx
+++ b/outputs/busca_saúde_coletiva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,11 +475,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -493,15 +493,15 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8. Paciente do sexo masculino, 25 anos, procura atendimento na 
-atenção primária, devido a quadro de diarreia de início há 24 
-horas. Refere fezes aquosas, de grande volume, coloração 
-acinzentada, com bastante muco e com odor de peixe. Relata 
-estar apresentando bastantes cãibras em membros inferiores nas 
-últimas horas. Nega febre, sangue nas fezes ou dor abdominal. 
-Refere ter viagem recente ao Haiti. Ao exame físico, estava 
-desidratado, taquicárdico e com hipotensão postural. Foram 
-solicit</t>
+          <t>5. Um homem de 55 anos, diabético tipo II, hipertenso em 
+estágio III, em tratamento regular com insulina, metformina, 
+ramipril, anlodipino, indapamida e rosuvastatina, busca auxílio 
+médico referindo dispneia paroxística noturna, tosse seca, edema 
+de membros inferiores e cansaço aos pequenos esforços. Ao 
+exame físico, foi identificada turgência de jugulares, presença de 
+B3 e crepitações em ambas as bases pulmonares, com pressão 
+arterial de 130x70mmHg e frequência cardíaca de 87bpm. 
+Realiz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -564,11 +564,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -581,6 +581,97 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Paciente do sexo masculino, com diagnóstico de demência 
+há 5 anos e sem tratamento farmacológico no momento, chega 
+para consulta na Unidade Básica de Saúde trazido pela filha, que 
+é sua cuidadora. Ela relata que, há três dias, houve mudança no 
+comportamento do seu pai, que está agitado, inquieto e insistindo 
+em realizar tarefas que habitualmente não faz, como subir em 
+escadas móveis, usar o fogão e dirigir. Ela tem conseguido 
+acalmá-lo, mas está receosa que ele possa piorar, perder o </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11. Paciente do sexo feminino, 27 anos, portadora de valva 
+aórtica bicúspide, procura o atendimento médico queixando-se de 
+cansaço, tonteira aos esforços e três síncopes recentes aos 
+esforços. Durante o exame cardiovascular, nota-se pulso parvus, 
+hipofonese da segunda bulha, presença de bulha telediastólica e 
+sopro cardíaco. Considerando a valvopatia mais provável neste 
+caso, o sopro cardíaco auscultado é: 
+(A) Pré-sistólico em ruflar 
+(B) Protodiastólico aspirativo 
+(C) Telessistólico 
+</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>152</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>15. Paciente de 70 anos chega à Unidade Básica de Saúde 
 (UBS) acompanhado de sua esposa. Relata ao médico que na 
@@ -593,39 +684,128 @@
 esposa. É s</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>156</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20. Paciente de 83 anos chega à Unidade Básica de Saúde 
+trazido pela filha, que está preocupada porque ele tem se 
+desequilibrado com frequência, está mais dependente de outras 
+pessoas, solicitando favores que até há pouco tempo não 
+solicitava, além de estar emagrecendo, embora alimente-se bem. 
+Com o objetivo de fazer uma avaliação direcionada, a médica 
+decide por realizar a Avaliação Geriátrica Ampla, uma entrevista 
+sistematizada que visa melhorar o suporte ao paciente idoso, 
+priorizando</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>158</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>21. Homem de 45 anos, trabalhador rural, procura a Estratégia 
+de Saúde da Família devido a quadro típico de lombociatalgia à 
+direita, com cerca de 2 meses de evolução, que piora às 
+atividades laborais, porém não o impede de realizá-las. Nega 
+parestesias no membro e refere ter feito uso de “pomadas” para 
+tratamento do sintoma, sem melhora. Ao exame físico, apresenta 
+dor típica em trajeto de nervo ciático ao se elevar a perna direita, 
+estendida a 45 graus. A força muscular, bem como os refl</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>159</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>22. Durante um surto de dengue, com mais de 50 atendimentos 
 por dia de pacientes com a doença, chega um senhor de 55 anos, 
@@ -638,39 +818,39 @@
 (A) Manter o AAS e solicitar a transfus</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>161</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">23. Homem de 47 anos chega para consulta na UBS referindo 
 desmaio há cerca de 1 hora. Disse que já aconteceu 3 vezes e, 
@@ -683,39 +863,39 @@
 </t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>160</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>25. Menino, 2 meses de vida, sem antecedentes patológicos, é 
 levado pela mãe à Unidade de Pronto Atendimento com queixa de 
@@ -727,39 +907,129 @@
 hipotenso, pulsos finos, taquicárdico e com tempo de enchim</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>163</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>26. Recém-nascido, masculino, 7 dias de vida, foi trazido para 
+avaliação na Unidade Básica de Saúde devido a queixa de 
+tumefação em região escrotal à direita. Ao exame, observado 
+abaulamento em região escrotal à direita, translúcida, indolor e 
+irredutível. Assinale a alternativa correta em relação ao 
+diagnóstico e sua justificativa: 
+(A) Hérnia, por ser translúcida e à direita. 
+(B) Hérnia inguinal, por ser irredutível e indolor. 
+(C) Hidrocele, por ser indolor e ser em recém-nascido. 
+(D</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>164</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>27. Menino, cinco anos, comparece ao Pronto Atendimento com 
+sua mãe, com queixa de dor abdominal intermitente há mais de 2 
+meses. Concomitantemente apresenta hábito de evacuar a cada 
+três ou quatro dias, fezes ressecadas, com dor e esforço à 
+evacuação desde o desfralde e introdução de leite de vaca na 
+dieta. Refere episódios de “escape fecal” de até três vezes por 
+semana. O paciente não aceita todos os alimentos oferecidos, 
+recusando hortaliças, legumes e a maioria das frutas. Prefere lei</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>170</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>34. Menina de seis meses de vida chega ao pronto atendimento 
 com histórico de tosse, coriza, obstrução nasal de início há cerca 
@@ -771,85 +1041,172 @@
 frequência cardíaca de 70bpm e sinais de comprometimen</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>176</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38. Nutriz, mãe de uma lactente de dois meses de vida, 
-comparece a consulta de puericultura na UBSF para receber 
-orientações, pois apresenta mama direita com presença de 
-hiperemia, edema, calor e drenagem de secreção pelo mamilo. 
-Qual das seguintes afirmações está correta em relação à 
-continuidade da amamentação? 
-(A) A mastite sempre contraindica a amamentação, 
-independentemente das condições de drenagem. 
-(B) A amamentação deve ser completamente interrompida até 
-que a infecção esteja </t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>174</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>37. Menina, 4 anos, é atendida na unidade de saúde onde faz 
+acompanhamento médico por apresentar crises de chiado de 
+repetição e dermatite atópica, fazendo uso diário de corticoide 
+inalatório em dose baixa. A mãe relata tosse e taquipneia desde a 
+véspera, tendo iniciado beta 2 adrenérgico, porém não observou 
+melhora e agora a criança apresenta-se pálida, sonolenta, tiragem 
+intercostal e retração subdiafragmática, murmúrio vesicular rude 
+com tempo expiratório prolongado, sibilos expiratóri</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>177</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>39. Menina, 7 anos, é atendida na Unidade Básica de Saúde por 
+apresentar crises de cefaleia em região temporal, unilateral, 
+acompanhadas por fotofobia e vômitos, tendo duração média de 6 
+horas e havendo limitação às suas atividades quotidianas. Estes 
+episódios ocorrem uma vez a cada 7-10 dias. Nesta consulta, 
+encontra-se     assintomática     e tem exame     clínico     normal. 
+Considerando a hipótese principal e a frequência das crises, o 
+médico opta por iniciar medicação preventiva. Con</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>175</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>40. Criança do sexo masculino, 2 anos de idade é levada a 
+consulta em UBS devido a queixa de comportamento agitado e 
+irritabilidade. Mãe de 43 anos, pai de 50 anos, terceiro filho do 
+casal. Pais relatam que durante o primeiro ano de vida era um 
+bebê tranquilo e gostava de dormir sozinho. A partir do segundo 
+ano de vida apresentou agitação, choro incontrolável em 
+situações de frustração e/ou com barulho intenso (trovões, 
+festas), seletividade alimentar e estereotipias. Acham que fala 
+meno</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>179</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>42. Você é médico(a) em uma unidade de saúde e recebe uma 
 adolescente de 14 anos, trazida pelos pais para avaliação da 
@@ -862,39 +1219,84 @@
 cl</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>180</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43. Adolescente, sexo feminino, 12 anos, comparece à Unidade 
+Básica de Saúde para consulta com enfoque na promoção à 
+saúde. Ao verificar a caderneta de vacinação, constata-se nos 
+registros que as vacinas estão atualizadas até os cinco anos de 
+idade. Quais são os imunobiológicos recomendados para 
+atualização do cartão vacinal da adolescente, conforme o 
+Programa Nacional de Imunização do Ministério da Saúde? 
+(A) Vacina Meningo C, contra Dengue, dT, Pneumo 23. 
+(B) Vacina contra COVID-19, </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>186</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>49. Paciente do sexo masculino, 50 anos, encaminhado do 
 Pronto Atendimento Municipal para o Hospital de referência para 
@@ -906,39 +1308,84 @@
 abdômen inferior. Ao exame, hipocorado 2+/4+, fácies hipocráti</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>190</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>51. Uma paciente do sexo feminino de 47 anos é atendida na 
+Unidade Básica de Saúde, com queixa de sensação de plenitude 
+e queimação retroesternal pós-prandial, que piora em posição 
+supina. Ela tem algum alívio com antiácidos orais, mas os 
+sintomas recorrem rapidamente. Seu índice de massa corporal é 
+33kg/m2 (obesidade classe I), não fuma e consome bebida 
+alcoólica eventualmente. Não possui comorbidades, não 
+apresenta qualquer outra alteração à história ou exame clínico. 
+Em relação à hist</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>192</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
         <is>
           <t>52. Paciente do sexo feminino, 44 anos, procura o ambulatório 
 com queixa de dor abdominal epigástrica irradiada para o dorso, 
@@ -951,39 +1398,39 @@
 (Fonte: arquivo do au</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>191</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
         <is>
           <t>55. Paciente de 18 anos, sexo masculino, vítima de acidente 
 automobilístico. Após avaliação primária,     o paciente se 
@@ -996,39 +1443,84 @@
 real</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>193</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56. Você é o médico de uma Unidade Básica de Saúde e recebe 
+um paciente do sexo masculino, de 45 anos, com relato de 
+fraqueza e astenia progressivas e fezes escurecidas (melena) – a 
+melena ocorre ocasionalmente nos últimos 8 meses. O paciente 
+apresenta: frequência cardíaca 90bpm, pressão arterial 
+130x84mmHg, boa perfusão periférica. Está discretamente 
+hipocorado (+/++++). É etilista crônico e apresenta ao exame 
+físico sinais clínicos de hepatopatia crônica. Ele traz resultados de 
+exames </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>202</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
         <is>
           <t>67. Paciente do sexo masculino, 28 anos, previamente hígido, 
 foi vítima de acidente motocicleta versus caminhonete – o 
@@ -1042,39 +1534,130 @@
 (C) Acesso venoso central</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>208</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>71. Paciente do sexo masculino, 22 anos, procura atendimento 
+médico em Unidade Básica de Saúde do bairro onde mora. Relata 
+história de fratura do úmero direito há cerca de 6 meses e 
+apresenta uma deformidade em “mão caída” (impossibilidade de 
+realizar a extensão do punho). Qual a causa do achado no caso 
+descrito? 
+(A) Lesão do nervo axilar 
+(B) Lesão no nervo mediano 
+(C) Lesão do nervo radial 
+(D) Lesão do nervo ulnar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>209</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>72. Paciente do sexo masculino, 68 anos, agenda consulta em 
+Unidade Básica de Saúde onde faz acompanhamento, devido a 
+lombociatalgia crônica à direita. Leva exames complementares 
+realizados: tomografia computadorizada da coluna lombar, que 
+mostra hérnia de disco a nível de L5-S1, paracentral, à direita, e 
+eletroneuromiografia de membros inferiores, que mostra 
+evidências de radiculopatia crônica L5-S1 do lado direito, de 
+padrão misto axonal e desmielizante, sem sinais de desnervação 
+atual</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>211</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>74. Mariana, uma mulher trans de 52 anos de idade, procura 
 UBSF desejando informações sobre rastreamento de câncer de 
@@ -1087,174 +1670,129 @@
 inclusão mamária co</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>219</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>82. Paciente de 47 anos, G1Pn1, em consulta especializada no 
-ambulatório de ginecologia traz mamografia evidenciando 
-parênquima mamário com densidade fibrogranular, sem 
-alterações significativas, presença de imagem nodular de 
-aproximadamente 2cm, de contornos parcialmente definidos, em 
-quadrante súpero-lateral de mama direita. Mama esquerda 
-apresentando       parênquima       mamário       com densidade 
-fibroglandular,     sem evidência de imagens nodulares     ou 
-calcificações suspeitas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>222</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>84. Mulher de 26 anos de idade procura a UBSF solicitando 
-orientação em Planejamento Familiar, pois casou-se há 3 meses 
-e não deseja filhos no momento. Está em uso de preservativos, 
-mas deseja método com maior eficácia. Gostaria de utilizar pílula 
-anticoncepcional, mas foi orientada a procurar avaliação médica, 
-pois tem diagnóstico de diabetes melito e teve quadro de 
-trombose venosa profunda em membros inferiores há 1 ano, 
-estando em uso de anticoagulante oral até o presente. Qual a 
-orie</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>231</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>92. Mulher de 25 anos, está grávida de 26 semanas e vem à 
-consulta preocupada com o risco de parto prematuro, pois sua 
-irmã teve dois partos prematuros. Tem histórico de infecção 
-urinária recorrente durante a gravidez e relata aumento na 
-frequência de contrações uterinas nas últimas semanas. O exame 
-físico mostra colo uterino encurtado. A melhor conduta para 
-rastreamento e prevenção de prematuridade nessa paciente é: 
-(A) Repouso absoluto até o término da gestação. 
-(B) Antibiótico profi</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>220</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83. Paciente de 17 anos, sexo feminino, procura Unidade Básica 
+de Saúde, pois, diferentemente de suas colegas na escola, ainda 
+não menstruou. Refere que sua mãe teve menarca aos 13 anos e 
+sua irmã mais velha aos 12 anos. Nega uso de medicamentos, 
+doenças crônicas ou outras condições médicas conhecidas. Ao 
+exame físico, observa-se desenvolvimento M1P1. Não há outras 
+alterações significativas. A alteração mais comum que justifica o 
+atraso no desenvolvimento puberal desta paciente pode ser 
+</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>234</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>97. Criança, 7 anos, compareceu à Unidade Básica de Saúde 
+para atendimento médico acompanhado pela mãe, que notou 
+mudança em seu comportamento nos últimos dias. Ele sempre 
+fora uma criança extrovertida e alegre, passou a se comportar de 
+maneira retraída e introspectiva, além da mãe ter notado alguns 
+hematomas em suas pernas, braços e rosto. A mãe demonstra 
+preocupação e relata não entender a mudança repentina no 
+comportamento da criança, diz que se sente culpada por ter que 
+trabalhar o d</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>237</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>98. Homem, 28 anos, estava trabalhando no açougue e teve um 
 corte nas mãos. Chegou à Unidade Básica de Saúde com um 
@@ -1267,39 +1805,39 @@
 (B) Entre os critérios de prescrição de apoio medicame</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>235</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
         <is>
           <t>99. Uma Equipe Saúde da Família acompanha há anos uma 
 senhora de 53 anos, portadora de Diabetes Mellitus Tipo 2 que, 
@@ -1311,39 +1849,39 @@
 descreve a aplicação adequada do apoio matricial neste c</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>239</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
         <is>
           <t>102. Na última reunião do Conselho Municipal de Saúde (CMS), 
 foi discutido o novo modelo de cofinanciamento federal de custeio 
@@ -1356,39 +1894,39 @@
 programa</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>242</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>103. Um médico de família e comunidade atuante em uma 
 Estratégia Saúde da Família é solicitado pela enfermeira da 
@@ -1401,39 +1939,39 @@
 região. No hospit</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>240</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">104. Homem, 40 anos, tabagista, morador de município com 
 cerca de 39.000 habitantes, é acompanhado há anos pelo médico 
@@ -1447,39 +1985,83 @@
 </t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>241</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>105. Foi observado um aumento significativo na mortalidade de 
+crianças menores de um ano em um determinado município, 
+principalmente dentre aquelas acompanhadas pelo ambulatório 
+de otorrinolaringologia. A Secretaria de Saúde decidiu realizar um 
+estudo epidemiológico para analisar esses dados e identificar 
+possíveis causas e fatores de risco associados a esses óbitos. A 
+equipe de saúde está encarregada de realizar um diagnóstico 
+situacional e escolheu conduzir um estudo de coorte histórico</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
         <v>243</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">106. Mulher, 76 anos, tabagista, obesa, hipertensa, diagnóstico 
 recente de aterosclerose coronariana, apresentou quadro de dor 
@@ -1491,39 +2073,39 @@
 equipe acionou o Serviço de Atendimento Móvel de Urgência </t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>247</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
         <is>
           <t>108. Aline, 39 anos, procurou o Centro de Saúde de referência 
 com queixa de diarreia intermitente há aproximadamente 7 dias. 
@@ -1535,39 +2117,39 @@
 comunidade, próxima ao centro de saúde, sem condições básicas</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>248</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>109. Durante uma consulta na Atenção Primária, uma paciente 
 de 35 anos de idade, do sexo feminino, relata sentir-se 
@@ -1579,39 +2161,39 @@
 ecomapa?</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>245</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>110. Uma paciente de 61 anos de idade, do sexo feminino, é 
 diagnosticada com diabetes mellitus tipo 2 durante uma consulta 
@@ -1624,39 +2206,39 @@
 (A) A pressão arterial mais</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>246</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
         <is>
           <t>111. O Pacto pela Saúde de 2006 impactou a transferência de 
 recursos federais para os Estados e Municípios em blocos de 
@@ -1665,39 +2247,39 @@
 SUS. Em relação a esse pacto, podemos afirmar:</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>249</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
         <is>
           <t>112. Um paciente do sexo masculino, 54 anos, apresenta 
 quadro de chikungunya em fase subaguda. Ele relata dor articular 
@@ -1711,39 +2293,39 @@
 familiares, visto que a sobrecarga famil</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
         <v>252</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
         <is>
           <t>115. Paciente do sexo feminino, 14 anos, foi levada pela mãe à 
 UBS após tomar 4 comprimidos de dipirona como tentativa de 
@@ -1755,39 +2337,39 @@
 questionada sobre abusos e violências, negou e disse que</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
         <v>255</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
         <is>
           <t>118. Paciente de 55 anos, hipertenso, em uso de anlodipino 
 10mg uma vez ao dia, chega à Unidade Básica de Saúde com o 
@@ -1800,39 +2382,39 @@
 (B) Adicionar um diurético tiazídico ou</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
         <v>256</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
         <is>
           <t>119. Diego, 45 anos, chega à UBS muito ansioso, querendo 
 saber o que fazer. Relata que teve relação na noite anterior com 
@@ -1845,39 +2427,39 @@
 deve ser usad</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>257</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Saúde Coletiva</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Saúde Coletiva</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>120. Joana, uma mulher de 55 anos, nunca realizou exames 
 preventivos de câncer de colo de útero. Durante uma consulta de 
@@ -1890,17 +2472,17 @@
 r</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>enamed</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>unilagos</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>enamed</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>unilagos</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>2026</v>
       </c>
     </row>
